--- a/支持库/后端/办公文档支持库/表格文档/夹具/最小中文表格.xlsx
+++ b/支持库/后端/办公文档支持库/表格文档/夹具/最小中文表格.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>甲</t>
+          <t>示例文本</t>
         </is>
       </c>
     </row>
